--- a/Notes and data for listed articles/(row 1) data for 2024 Xu et al. /raw_data/data_for_time_spend_in_target_quadrant_and_platform_crossed.xlsx
+++ b/Notes and data for listed articles/(row 1) data for 2024 Xu et al. /raw_data/data_for_time_spend_in_target_quadrant_and_platform_crossed.xlsx
@@ -117,7 +117,7 @@
     <xdr:ext cx="3190875" cy="2447925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -173,7 +173,7 @@
     <xdr:ext cx="3190875" cy="2447925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -229,7 +229,7 @@
     <xdr:ext cx="3248025" cy="2800350"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/Notes and data for listed articles/(row 1) data for 2024 Xu et al. /raw_data/data_for_time_spend_in_target_quadrant_and_platform_crossed.xlsx
+++ b/Notes and data for listed articles/(row 1) data for 2024 Xu et al. /raw_data/data_for_time_spend_in_target_quadrant_and_platform_crossed.xlsx
@@ -117,7 +117,7 @@
     <xdr:ext cx="3190875" cy="2447925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -173,7 +173,7 @@
     <xdr:ext cx="3190875" cy="2447925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
